--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT VEDANT\Advance excel1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085106FF-3E93-4E4B-9977-BED890098769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B188C8E-1D56-43B2-8F99-4EECF51DF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMart_Sales_Data" sheetId="6" r:id="rId1"/>
     <sheet name="CustomeList" sheetId="4" r:id="rId2"/>
     <sheet name="FlashFill" sheetId="3" r:id="rId3"/>
     <sheet name="IF_Statements" sheetId="5" r:id="rId4"/>
+    <sheet name="VlookUp" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CustomeList!$B$11:$B$17</definedName>
@@ -43,14 +44,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="666">
   <si>
     <t>Region</t>
   </si>
@@ -2036,6 +2037,18 @@
   </si>
   <si>
     <t>Total Sales using subtotal</t>
+  </si>
+  <si>
+    <t>EmployeeID</t>
+  </si>
+  <si>
+    <t>Bonus_Amount</t>
+  </si>
+  <si>
+    <t>Using Vlookup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using Index </t>
   </si>
 </sst>
 </file>
@@ -2045,13 +2058,20 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2212,7 +2232,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2306,6 +2326,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F4F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2435,16 +2467,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2452,7 +2484,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2464,98 +2496,111 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -30155,7 +30200,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B11:B17" xr:uid="{DD2C2FD5-8379-4925-B2E3-1BBDDF1E9A2D}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -30860,7 +30905,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E3:F8">
     <sortCondition ref="E3:E8" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>3000</formula>
@@ -30874,4 +30919,218 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F8B828-58BD-4DF8-81C9-FD233710EB03}">
+  <dimension ref="A2:H18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>616</v>
+      </c>
+      <c r="G2">
+        <f>MATCH("sales",A2:E2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="C3" s="11">
+        <v>70000</v>
+      </c>
+      <c r="D3" s="14">
+        <f>IF(C3&gt;=75000,15%,IF(C3&gt;=70000,10%,IF(C3&gt;=50000,5%,IF(C3&lt;50000,0))))</f>
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="15">
+        <f>C3*D3</f>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="C4" s="11">
+        <v>50000</v>
+      </c>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D7" si="0">IF(C4&gt;=75000,15%,IF(C4&gt;=70000,10%,IF(C4&gt;=50000,5%,IF(C4&lt;50000,0))))</f>
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:E7" si="1">C4*D4</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="C5" s="11">
+        <v>45000</v>
+      </c>
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" s="11">
+        <v>75000</v>
+      </c>
+      <c r="D6" s="14">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" si="1"/>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="C7" s="11">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="14">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="15">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="82" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="80" t="s">
+        <v>662</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>569</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="79">
+        <v>1002</v>
+      </c>
+      <c r="C11" s="79">
+        <f>VLOOKUP(B11,A3:E7,MATCH(C2,A2:E2,0),FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="D11" s="79">
+        <f>VLOOKUP(B11,A3:E7,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>2500</v>
+      </c>
+      <c r="H11">
+        <f>MATCH(C2,A2:E2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="83" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="80" t="s">
+        <v>662</v>
+      </c>
+      <c r="C14" s="62" t="s">
+        <v>569</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="78">
+        <v>1002</v>
+      </c>
+      <c r="C15" s="84">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(C2,A2:E2,0))</f>
+        <v>50000</v>
+      </c>
+      <c r="D15" s="84">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(E2,A2:E2,0))</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <f>MATCH(C4,C2:C7,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="81" t="s">
+        <v>569</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11 B15" xr:uid="{39053AA3-D821-4D8A-A0A0-34B442E6C155}">
+      <formula1>$A$3:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT VEDANT\Advance excel1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B188C8E-1D56-43B2-8F99-4EECF51DF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECD7B5A-1F21-499A-AFE0-EAB6F978737C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMart_Sales_Data" sheetId="6" r:id="rId1"/>
@@ -18,14 +18,21 @@
     <sheet name="FlashFill" sheetId="3" r:id="rId3"/>
     <sheet name="IF_Statements" sheetId="5" r:id="rId4"/>
     <sheet name="VlookUp" sheetId="7" r:id="rId5"/>
+    <sheet name="Hlookup" sheetId="8" r:id="rId6"/>
+    <sheet name="Indirect" sheetId="9" r:id="rId7"/>
+    <sheet name="Indirect3" sheetId="10" r:id="rId8"/>
+    <sheet name="Data Validation" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CustomeList!$B$11:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DMart_Sales_Data!$A$1:$P$499</definedName>
+    <definedName name="appless">Indirect3!$B$2:$B$6</definedName>
+    <definedName name="bananass">Indirect3!$C$2:$C$6</definedName>
     <definedName name="categoryy">DMart_Sales_Data!$D$2:$D$499</definedName>
     <definedName name="customerrr">DMart_Sales_Data!$K$2:$K$499</definedName>
     <definedName name="deliverydatee">DMart_Sales_Data!$J$2:$J$499</definedName>
     <definedName name="discountt">DMart_Sales_Data!$G$2:$G$499</definedName>
+    <definedName name="lemons">Indirect3!$D$2:$D$6</definedName>
     <definedName name="orderdatee">DMart_Sales_Data!$I$2:$I$499</definedName>
     <definedName name="orderr">DMart_Sales_Data!$A$2:$A$499</definedName>
     <definedName name="paymenttt">DMart_Sales_Data!$M$2:$M$499</definedName>
@@ -44,14 +51,36 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="700">
   <si>
     <t>Region</t>
   </si>
@@ -2049,6 +2078,108 @@
   </si>
   <si>
     <t xml:space="preserve">Using Index </t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Vlookup</t>
+  </si>
+  <si>
+    <t>Hlookup</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>R10C1</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Apples</t>
+  </si>
+  <si>
+    <t>Bananas</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Neha</t>
+  </si>
+  <si>
+    <t>Ketan</t>
+  </si>
+  <si>
+    <t>Sunil</t>
+  </si>
+  <si>
+    <t>Pooja</t>
+  </si>
+  <si>
+    <t>lemons</t>
+  </si>
+  <si>
+    <t>Fruit:</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>OrderID</t>
   </si>
 </sst>
 </file>
@@ -2060,11 +2191,25 @@
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2168,22 +2313,26 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2231,8 +2380,22 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2341,8 +2504,25 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2464,19 +2644,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2484,7 +2691,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2496,113 +2703,126 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="11" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2838,10 +3058,13 @@
   <dimension ref="A1:Y499"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -4790,8 +5013,12 @@
         <v>40</v>
       </c>
       <c r="Q32" s="38"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="23"/>
+      <c r="R32" s="96" t="s">
+        <v>699</v>
+      </c>
+      <c r="S32" s="96" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="29" t="s">
@@ -4844,8 +5071,13 @@
         <v>16</v>
       </c>
       <c r="Q33" s="33"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
+      <c r="R33" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" s="50">
+        <f>VLOOKUP(R33,A2:P499,MATCH(S32,A1:P1,0),FALSE)</f>
+        <v>1160.8599999999999</v>
+      </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
@@ -30033,6 +30265,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S32" xr:uid="{19BCF2D0-C5A9-4F66-9E05-88E16655DA39}">
+      <formula1>$A$1:$P$1</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R33" xr:uid="{D0553110-5A6F-4237-9862-C097CEBD2AC3}">
+      <formula1>orderr</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -30200,7 +30440,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B11:B17" xr:uid="{DD2C2FD5-8379-4925-B2E3-1BBDDF1E9A2D}"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -30905,7 +31145,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E3:F8">
     <sortCondition ref="E3:E8" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>3000</formula>
@@ -30923,13 +31163,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F8B828-58BD-4DF8-81C9-FD233710EB03}">
-  <dimension ref="A2:H18"/>
+  <dimension ref="A2:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -31047,6 +31289,10 @@
         <f t="shared" si="1"/>
         <v>2750</v>
       </c>
+      <c r="H7">
+        <f>VLOOKUP(B11,A3:E7,3,FALSE)</f>
+        <v>55000</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="82" t="s">
@@ -31063,18 +31309,32 @@
       <c r="D10" s="62" t="s">
         <v>616</v>
       </c>
+      <c r="F10" t="s">
+        <v>569</v>
+      </c>
+      <c r="G10" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="79">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C11" s="79">
         <f>VLOOKUP(B11,A3:E7,MATCH(C2,A2:E2,0),FALSE)</f>
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="D11" s="79">
         <f>VLOOKUP(B11,A3:E7,MATCH(E2,A2:E2,0),FALSE)</f>
-        <v>2500</v>
+        <v>2750</v>
+      </c>
+      <c r="F11">
+        <f>VLOOKUP(B11,A3:E7,MATCH(C2,A2:E2,0),FALSE)</f>
+        <v>55000</v>
+      </c>
+      <c r="G11">
+        <f>VLOOKUP(B11,A3:E7,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>2750</v>
       </c>
       <c r="H11">
         <f>MATCH(C2,A2:E2,0)</f>
@@ -31096,18 +31356,38 @@
       <c r="D14" s="62" t="s">
         <v>616</v>
       </c>
+      <c r="F14" s="84" t="s">
+        <v>657</v>
+      </c>
+      <c r="G14" s="84" t="s">
+        <v>569</v>
+      </c>
+      <c r="H14" s="84" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="78">
         <v>1002</v>
       </c>
-      <c r="C15" s="84">
+      <c r="C15" s="79">
         <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(C2,A2:E2,0))</f>
         <v>50000</v>
       </c>
-      <c r="D15" s="84">
+      <c r="D15" s="79">
         <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(E2,A2:E2,0))</f>
         <v>2500</v>
+      </c>
+      <c r="F15" s="47">
+        <v>1003</v>
+      </c>
+      <c r="G15" s="47">
+        <f>VLOOKUP(F15,A3:E7,MATCH(C2,A2:E2,0),FALSE)</f>
+        <v>45000</v>
+      </c>
+      <c r="H15" s="47">
+        <f>VLOOKUP(F15,A3:E7,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -31124,13 +31404,710 @@
         <v>663</v>
       </c>
     </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),3)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(C2,A2:E2,0))</f>
+        <v>50000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11 B15" xr:uid="{39053AA3-D821-4D8A-A0A0-34B442E6C155}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11 B15 F15" xr:uid="{39053AA3-D821-4D8A-A0A0-34B442E6C155}">
       <formula1>$A$3:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0657ECA-56F1-463D-9BFF-2A8D508F90E7}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="86"/>
+      <c r="B2" s="86" t="s">
+        <v>666</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>667</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>668</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>669</v>
+      </c>
+      <c r="F2" s="86" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="86" t="s">
+        <v>670</v>
+      </c>
+      <c r="B3" s="86">
+        <v>100</v>
+      </c>
+      <c r="C3" s="86">
+        <v>585</v>
+      </c>
+      <c r="D3" s="86">
+        <v>333</v>
+      </c>
+      <c r="E3" s="86">
+        <v>745</v>
+      </c>
+      <c r="F3" s="86">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="86" t="s">
+        <v>671</v>
+      </c>
+      <c r="B4" s="86">
+        <v>100</v>
+      </c>
+      <c r="C4" s="86">
+        <v>500</v>
+      </c>
+      <c r="D4" s="86">
+        <v>600</v>
+      </c>
+      <c r="E4" s="86">
+        <v>700</v>
+      </c>
+      <c r="F4" s="86">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="86" t="s">
+        <v>569</v>
+      </c>
+      <c r="B5" s="86">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="86">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="86">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="86">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="86">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="86" t="s">
+        <v>672</v>
+      </c>
+      <c r="B6" s="86">
+        <v>400</v>
+      </c>
+      <c r="C6" s="86">
+        <v>500</v>
+      </c>
+      <c r="D6" s="86">
+        <v>300</v>
+      </c>
+      <c r="E6" s="86">
+        <v>300</v>
+      </c>
+      <c r="F6" s="86">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="85" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="87" t="s">
+        <v>580</v>
+      </c>
+      <c r="C9" s="87" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="88" t="s">
+        <v>672</v>
+      </c>
+      <c r="C10" s="88">
+        <f>HLOOKUP($C$9,$A$2:$F$6,MATCH(B10,$A$2:$A$6,0),FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E10" s="85" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="88" t="s">
+        <v>671</v>
+      </c>
+      <c r="C11" s="88">
+        <f t="shared" ref="C11:C12" si="0">HLOOKUP($C$9,$A$2:$F$6,MATCH(B11,$A$2:$A$6,0),FALSE)</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="88" t="s">
+        <v>569</v>
+      </c>
+      <c r="C12" s="88">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="E12" s="85" t="s">
+        <v>569</v>
+      </c>
+      <c r="F12">
+        <f>VLOOKUP(A5,A3:F6,MATCH(F2,A2:F2,0),FALSE)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <f>HLOOKUP(C9,A2:F6,MATCH(B10,A2:A6,0),FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="28" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{60D20A43-1DFC-4836-9654-CE581DCE640F}">
+      <formula1>$B$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10 E12" xr:uid="{F4AF710C-1BF0-4501-84F7-6B8C8CDD1104}">
+      <formula1>$A$3:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22C2AC5B-8FAE-4BB3-8A63-D3EA8BD41129}">
+  <dimension ref="A3:H11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="C3" cm="1">
+        <f t="array" aca="1" ref="C3" ca="1">INDIRECT("A3")+10</f>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G3" t="s">
+        <v>679</v>
+      </c>
+      <c r="H3" t="str">
+        <f>F3&amp;"  "&amp;G3</f>
+        <v>Ankit  Sharma</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C6" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">INDIRECT(B6)+100</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>677</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">INDIRECT(C11,FALSE)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>333</v>
+      </c>
+      <c r="C11" t="s">
+        <v>678</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">INDIRECT("A10",TRUE)</f>
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B57865-2B8E-4F41-9FD9-0B8C810D50A2}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="89" t="s">
+        <v>680</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>681</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>687</v>
+      </c>
+      <c r="F1" s="90" t="s">
+        <v>688</v>
+      </c>
+      <c r="G1" s="90" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B2">
+        <v>55</v>
+      </c>
+      <c r="C2">
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>689</v>
+      </c>
+      <c r="G2">
+        <f ca="1">SUM(INDIRECT(G1))</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B3">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>690</v>
+      </c>
+      <c r="G3">
+        <f ca="1">AVERAGE(INDIRECT(G1))</f>
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>684</v>
+      </c>
+      <c r="B4">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G4">
+        <f ca="1">MAX(INDIRECT(G1))</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B5">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>686</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB98AFA-FFBE-4379-8AE2-A7FB4F5CE163}">
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>698</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>694</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>697</v>
+      </c>
+      <c r="E1" s="94" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="47">
+        <v>21</v>
+      </c>
+      <c r="B2" s="47">
+        <v>1235</v>
+      </c>
+      <c r="C2" s="47">
+        <v>2</v>
+      </c>
+      <c r="D2" s="93">
+        <v>46217</v>
+      </c>
+      <c r="E2" s="47">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="47">
+        <v>18</v>
+      </c>
+      <c r="B3" s="95"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="93">
+        <v>46218</v>
+      </c>
+      <c r="E3" s="47"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="47">
+        <v>60</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="93">
+        <v>46219</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="G4" s="91" t="s">
+        <v>695</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="47">
+        <v>21</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="93">
+        <v>46220</v>
+      </c>
+      <c r="E5" s="47"/>
+      <c r="G5" s="91" t="s">
+        <v>696</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47">
+        <v>2</v>
+      </c>
+      <c r="D6" s="93">
+        <v>46221</v>
+      </c>
+      <c r="E6" s="47"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="47">
+        <v>12</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47">
+        <v>6</v>
+      </c>
+      <c r="D7" s="93">
+        <v>46222</v>
+      </c>
+      <c r="E7" s="47"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="47">
+        <v>65</v>
+      </c>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="93">
+        <v>46223</v>
+      </c>
+      <c r="E8" s="47"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="47">
+        <v>54</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="93">
+        <v>46224</v>
+      </c>
+      <c r="E9" s="47"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="47">
+        <v>60</v>
+      </c>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="93">
+        <v>46225</v>
+      </c>
+      <c r="E10" s="47"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>25</v>
+      </c>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="93">
+        <v>46226</v>
+      </c>
+      <c r="E11" s="47"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="47"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="93">
+        <v>46227</v>
+      </c>
+      <c r="E12" s="47"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="47"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="H15" s="92"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="47"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="47"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="47"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Age Error" error="The Age Enter is not within range" promptTitle="Age Restrictions" prompt="Enter Age Between 18 to 60" sqref="A1:A1048576" xr:uid="{08316BA6-B817-4F1C-825A-DFF7DE1C4052}">
+      <formula1>18</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Quantity Error" error="Quantity is Invalid" promptTitle="Quantity Restrictions" prompt="Enter Quantity Between 2 to 10" sqref="C1:C1048576" xr:uid="{9F624DB0-9210-4B31-9C0A-704E211CB2DF}">
+      <formula1>$H$4</formula1>
+      <formula2>$H$5</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Error" error="Date Is Invalid, please enter valid date" sqref="D2:D30" xr:uid="{70D41EFF-5C72-49D3-9490-1EF0CCD350D3}">
+      <formula1>46218</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="marks error" error="Marks are invalid , please enter valid marks" sqref="E2 E4:E30 E3" xr:uid="{9AC0B90E-A198-4D89-BC52-DFE425ABA5E7}">
+      <formula1>AND(E2&gt;40,E2&lt;=75)</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="INCORRECT OTP" error="Enter correct otp" promptTitle="OTP" prompt="Enter OTP recieved four characters" sqref="B2:B30" xr:uid="{6F3AF7DC-32C6-4564-BEFE-E1767EE2B45D}">
+      <formula1>4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT VEDANT\Advance excel1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECD7B5A-1F21-499A-AFE0-EAB6F978737C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8BECD8-6B8C-4E30-99C9-4D2D8906DC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2186,12 +2186,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2392,6 +2393,12 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2671,10 +2678,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2818,11 +2826,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -5013,10 +5022,10 @@
         <v>40</v>
       </c>
       <c r="Q32" s="38"/>
-      <c r="R32" s="96" t="s">
+      <c r="R32" s="95" t="s">
         <v>699</v>
       </c>
-      <c r="S32" s="96" t="s">
+      <c r="S32" s="95" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5074,7 +5083,7 @@
       <c r="R33" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="S33" s="50">
+      <c r="S33" s="96">
         <f>VLOOKUP(R33,A2:P499,MATCH(S32,A1:P1,0),FALSE)</f>
         <v>1160.8599999999999</v>
       </c>
@@ -31842,7 +31851,7 @@
       <c r="A3" s="47">
         <v>18</v>
       </c>
-      <c r="B3" s="95"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="47"/>
       <c r="D3" s="93">
         <v>46218</v>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT VEDANT\Advance excel1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8BECD8-6B8C-4E30-99C9-4D2D8906DC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41667B3D-8E07-4187-9EC0-04EB6D72CB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4715" uniqueCount="700">
   <si>
     <t>Region</t>
   </si>
@@ -2684,7 +2684,7 @@
     <xf numFmtId="0" fontId="27" fillId="19" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2828,6 +2828,7 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
@@ -3074,13 +3075,15 @@
     <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.88671875" customWidth="1"/>
     <col min="18" max="18" width="47" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
@@ -4968,7 +4971,9 @@
         <v>34</v>
       </c>
       <c r="Q31" s="33"/>
-      <c r="R31" s="23"/>
+      <c r="R31" s="97" t="s">
+        <v>664</v>
+      </c>
       <c r="S31" s="23"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
